--- a/testData/DDT_testdata.xlsx
+++ b/testData/DDT_testdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bba80875e260e8e3/Desktop/OrangeHRM_Test_Suite/testData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="246" documentId="8_{F5AB6998-FAF7-4A82-A8FC-A21EFAED1A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DB76534-1AEF-41B6-AE85-613A8D6E941E}"/>
+  <xr:revisionPtr revIDLastSave="287" documentId="8_{F5AB6998-FAF7-4A82-A8FC-A21EFAED1A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D226D60-951D-41C8-B358-CC8F611DD434}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{4CB12ADF-4430-4E69-A35C-A24127896C07}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="118">
   <si>
     <t>File Path</t>
   </si>
@@ -327,13 +327,70 @@
     <t>Schedule Interview and Reject</t>
   </si>
   <si>
-    <t xml:space="preserve">Offer Accept and </t>
-  </si>
-  <si>
     <t>Interview pass/fail/reject</t>
   </si>
   <si>
     <t>Payroll Administrator</t>
+  </si>
+  <si>
+    <t>Kelly</t>
+  </si>
+  <si>
+    <t>Erin</t>
+  </si>
+  <si>
+    <t>Hannon</t>
+  </si>
+  <si>
+    <t>kelly@dundermifflin.com</t>
+  </si>
+  <si>
+    <t>Current Receptionist</t>
+  </si>
+  <si>
+    <t>Angella</t>
+  </si>
+  <si>
+    <t>Noelle</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>angella@dundermifflin.com</t>
+  </si>
+  <si>
+    <t>Second Round of Interview</t>
+  </si>
+  <si>
+    <t>Bailey</t>
+  </si>
+  <si>
+    <t>Howard</t>
+  </si>
+  <si>
+    <t>Digitization expert</t>
+  </si>
+  <si>
+    <t>ryan@dunddermifflin.com</t>
+  </si>
+  <si>
+    <t>Ryan</t>
+  </si>
+  <si>
+    <t>Gabriel</t>
+  </si>
+  <si>
+    <t>Susan</t>
+  </si>
+  <si>
+    <t>Lewis</t>
+  </si>
+  <si>
+    <t>lewis@dundermifflin.com</t>
+  </si>
+  <si>
+    <t>Hired</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1077,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B4EA1A-0C17-449A-9C5C-7637EE779B83}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" customWidth="1"/>
@@ -1081,7 +1138,7 @@
         <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F2">
         <v>8786564</v>
@@ -1113,7 +1170,7 @@
         <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F3">
         <v>7987643</v>
@@ -1145,7 +1202,7 @@
         <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F4">
         <v>9086954</v>
@@ -1177,7 +1234,7 @@
         <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F5">
         <v>9090294</v>
@@ -1189,7 +1246,7 @@
         <v>85</v>
       </c>
       <c r="I5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J5" t="s">
         <v>86</v>
@@ -1209,7 +1266,7 @@
         <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F6">
         <v>9088765</v>
@@ -1221,10 +1278,135 @@
         <v>64</v>
       </c>
       <c r="I6" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="J6" t="s">
         <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F7">
+        <v>1223545</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" t="s">
+        <v>64</v>
+      </c>
+      <c r="I7" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8">
+        <v>9567855</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E9" t="s">
+        <v>97</v>
+      </c>
+      <c r="F9">
+        <v>2367855</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" t="s">
+        <v>85</v>
+      </c>
+      <c r="J9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10">
+        <v>7337955</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" t="s">
+        <v>117</v>
+      </c>
+      <c r="J10" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1234,6 +1416,10 @@
     <hyperlink ref="D4" r:id="rId3" xr:uid="{17EF0CF1-022E-48E5-9738-BC62C519B7E9}"/>
     <hyperlink ref="D5" r:id="rId4" xr:uid="{99619FBD-99BE-481A-BB70-79ECF82AE1D6}"/>
     <hyperlink ref="D6" r:id="rId5" xr:uid="{5E01DD81-9C36-4E2C-83A9-25C2BE2F9BEF}"/>
+    <hyperlink ref="D7" r:id="rId6" xr:uid="{079FF018-7EA3-4A84-B92A-3085145A6ED2}"/>
+    <hyperlink ref="D8" r:id="rId7" xr:uid="{B9FA7CB8-867D-4293-BD0A-C8EE2693F854}"/>
+    <hyperlink ref="D9" r:id="rId8" xr:uid="{A03A9FAC-3976-402D-9C93-052D78B3F37B}"/>
+    <hyperlink ref="D10" r:id="rId9" xr:uid="{21DDBB41-3181-44BA-939D-5C78F237A4A6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/testData/DDT_testdata.xlsx
+++ b/testData/DDT_testdata.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bba80875e260e8e3/Desktop/OrangeHRM_Test_Suite/testData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="287" documentId="8_{F5AB6998-FAF7-4A82-A8FC-A21EFAED1A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D226D60-951D-41C8-B358-CC8F611DD434}"/>
+  <xr:revisionPtr revIDLastSave="375" documentId="8_{F5AB6998-FAF7-4A82-A8FC-A21EFAED1A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9016D8AA-C7D2-4D1F-ACBF-BA5E4A468476}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{4CB12ADF-4430-4E69-A35C-A24127896C07}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{4CB12ADF-4430-4E69-A35C-A24127896C07}"/>
   </bookViews>
   <sheets>
     <sheet name="Resume_File_Paths_One" sheetId="1" r:id="rId1"/>
     <sheet name="Resume_File_Paths_Two" sheetId="2" r:id="rId2"/>
     <sheet name="Email_IDs" sheetId="3" r:id="rId3"/>
     <sheet name="Candidate_List" sheetId="4" r:id="rId4"/>
+    <sheet name="Contact_Numbers" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="159">
   <si>
     <t>File Path</t>
   </si>
@@ -372,9 +373,6 @@
     <t>Digitization expert</t>
   </si>
   <si>
-    <t>ryan@dunddermifflin.com</t>
-  </si>
-  <si>
     <t>Ryan</t>
   </si>
   <si>
@@ -391,6 +389,132 @@
   </si>
   <si>
     <t>Hired</t>
+  </si>
+  <si>
+    <t>Alex</t>
+  </si>
+  <si>
+    <t>Flenderson</t>
+  </si>
+  <si>
+    <t>Stanley</t>
+  </si>
+  <si>
+    <t>Hudson</t>
+  </si>
+  <si>
+    <t>Odoi</t>
+  </si>
+  <si>
+    <t>ryan@dundermifflin.com</t>
+  </si>
+  <si>
+    <t>stanley@dundermifflin.com</t>
+  </si>
+  <si>
+    <t>Meredith</t>
+  </si>
+  <si>
+    <t>Cole</t>
+  </si>
+  <si>
+    <t>Palmer</t>
+  </si>
+  <si>
+    <t>meredith@dundermifflin.com</t>
+  </si>
+  <si>
+    <t>Oscar</t>
+  </si>
+  <si>
+    <t>Bob</t>
+  </si>
+  <si>
+    <t>oscar@dundermifflin.com</t>
+  </si>
+  <si>
+    <t>Toby</t>
+  </si>
+  <si>
+    <t>toby@dundermifflin.com</t>
+  </si>
+  <si>
+    <t>Martinez</t>
+  </si>
+  <si>
+    <t>Ex-HR</t>
+  </si>
+  <si>
+    <t>Cross Word Specialist</t>
+  </si>
+  <si>
+    <t>Accountant</t>
+  </si>
+  <si>
+    <t>contact_num_1</t>
+  </si>
+  <si>
+    <t>contact_num_2</t>
+  </si>
+  <si>
+    <t>contact_num_3</t>
+  </si>
+  <si>
+    <t>contact_num_4</t>
+  </si>
+  <si>
+    <t>contact_num_5</t>
+  </si>
+  <si>
+    <t>contact_num_6</t>
+  </si>
+  <si>
+    <t>(+91)573831</t>
+  </si>
+  <si>
+    <t>(0)91723583</t>
+  </si>
+  <si>
+    <t>+8282622</t>
+  </si>
+  <si>
+    <t>92929!</t>
+  </si>
+  <si>
+    <t>(+91)573$</t>
+  </si>
+  <si>
+    <t>182929/1910</t>
+  </si>
+  <si>
+    <t>(+91)573831/7282</t>
+  </si>
+  <si>
+    <t>181327/abcd</t>
+  </si>
+  <si>
+    <t>contact_num_7</t>
+  </si>
+  <si>
+    <t>contact_num_8</t>
+  </si>
+  <si>
+    <t>contact_num_9</t>
+  </si>
+  <si>
+    <t>contact_num_10</t>
+  </si>
+  <si>
+    <t>acdfff</t>
+  </si>
+  <si>
+    <t>98788&amp;&amp;</t>
+  </si>
+  <si>
+    <t>contact_num_11</t>
+  </si>
+  <si>
+    <t>contact_num_12</t>
   </si>
 </sst>
 </file>
@@ -455,7 +579,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -463,6 +587,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1077,7 +1208,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B4EA1A-0C17-449A-9C5C-7637EE779B83}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" customWidth="1"/>
@@ -1350,7 +1481,7 @@
     </row>
     <row r="9" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B9" t="s">
         <v>108</v>
@@ -1359,7 +1490,7 @@
         <v>109</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="E9" t="s">
         <v>97</v>
@@ -1379,16 +1510,16 @@
     </row>
     <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B10" t="s">
         <v>113</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>114</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="E10" t="s">
         <v>97</v>
@@ -1403,10 +1534,126 @@
         <v>85</v>
       </c>
       <c r="I10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J10" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E11" t="s">
+        <v>97</v>
+      </c>
+      <c r="F11">
+        <v>7000754</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" t="s">
+        <v>85</v>
+      </c>
+      <c r="J11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12">
+        <v>9272433</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" t="s">
+        <v>85</v>
+      </c>
+      <c r="J12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E13" t="s">
+        <v>97</v>
+      </c>
+      <c r="F13">
+        <v>8916344</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" t="s">
+        <v>85</v>
+      </c>
+      <c r="J13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>128</v>
+      </c>
+      <c r="B14" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" t="s">
+        <v>133</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E14" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14">
+        <v>9805132</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" t="s">
+        <v>85</v>
+      </c>
+      <c r="J14" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1420,7 +1667,170 @@
     <hyperlink ref="D8" r:id="rId7" xr:uid="{B9FA7CB8-867D-4293-BD0A-C8EE2693F854}"/>
     <hyperlink ref="D9" r:id="rId8" xr:uid="{A03A9FAC-3976-402D-9C93-052D78B3F37B}"/>
     <hyperlink ref="D10" r:id="rId9" xr:uid="{21DDBB41-3181-44BA-939D-5C78F237A4A6}"/>
+    <hyperlink ref="D11" r:id="rId10" xr:uid="{141E7B60-CF90-4C36-BD72-7A5BFA20D60B}"/>
+    <hyperlink ref="D12" r:id="rId11" xr:uid="{2DA94E17-E9B6-4D75-B04E-412EB89AB285}"/>
+    <hyperlink ref="D13" r:id="rId12" xr:uid="{DCACC0EF-32D7-480C-BBC2-9093982F8066}"/>
+    <hyperlink ref="D14" r:id="rId13" xr:uid="{D5B91B6D-1CD6-4417-B97B-58702E8D633A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{736EB4DE-8806-42E9-9F5E-674FFDC6194E}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30.5546875" customWidth="1"/>
+    <col min="2" max="2" width="33.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2" s="6">
+        <v>8273573</v>
+      </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>154</v>
+      </c>
+      <c r="B11" s="7">
+        <v>917789392</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>157</v>
+      </c>
+      <c r="B12" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>158</v>
+      </c>
+      <c r="B13" t="s">
+        <v>156</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/testData/DDT_testdata.xlsx
+++ b/testData/DDT_testdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bba80875e260e8e3/Desktop/OrangeHRM_Test_Suite/testData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="375" documentId="8_{F5AB6998-FAF7-4A82-A8FC-A21EFAED1A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9016D8AA-C7D2-4D1F-ACBF-BA5E4A468476}"/>
+  <xr:revisionPtr revIDLastSave="443" documentId="8_{F5AB6998-FAF7-4A82-A8FC-A21EFAED1A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F58E8F3D-6CC5-4ADA-AED3-423AE279AE85}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{4CB12ADF-4430-4E69-A35C-A24127896C07}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{4CB12ADF-4430-4E69-A35C-A24127896C07}"/>
   </bookViews>
   <sheets>
     <sheet name="Resume_File_Paths_One" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Email_IDs" sheetId="3" r:id="rId3"/>
     <sheet name="Candidate_List" sheetId="4" r:id="rId4"/>
     <sheet name="Contact_Numbers" sheetId="5" r:id="rId5"/>
+    <sheet name="Date_Formats" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="196">
   <si>
     <t>File Path</t>
   </si>
@@ -515,6 +516,117 @@
   </si>
   <si>
     <t>contact_num_12</t>
+  </si>
+  <si>
+    <t>yyyy-dd-mm</t>
+  </si>
+  <si>
+    <t>mm-dd-yyyy</t>
+  </si>
+  <si>
+    <t>yyyy-mm-dd</t>
+  </si>
+  <si>
+    <t>yyyy/dd/mm</t>
+  </si>
+  <si>
+    <t>mm/dd/yyyy</t>
+  </si>
+  <si>
+    <t>yyyy/mm/dd</t>
+  </si>
+  <si>
+    <t>dd/mm/yyyy</t>
+  </si>
+  <si>
+    <t>mm-yyyy-dd</t>
+  </si>
+  <si>
+    <t>dd-yyyy-mm</t>
+  </si>
+  <si>
+    <t>mm/yyyy/dd</t>
+  </si>
+  <si>
+    <t>dd/yyyy/mm</t>
+  </si>
+  <si>
+    <t>ddmmyyyy</t>
+  </si>
+  <si>
+    <t>yyyyddmm</t>
+  </si>
+  <si>
+    <t>mmddyyyy</t>
+  </si>
+  <si>
+    <t>yyyymmdd</t>
+  </si>
+  <si>
+    <t>ddyyyymm</t>
+  </si>
+  <si>
+    <t>mmyyyydd</t>
+  </si>
+  <si>
+    <t>dd-mm-yyyy</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>12-31-2025</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>2025/31/12</t>
+  </si>
+  <si>
+    <t>12/31/2025</t>
+  </si>
+  <si>
+    <t>2025/12/31</t>
+  </si>
+  <si>
+    <t>12/12/2025</t>
+  </si>
+  <si>
+    <t>12-2025-31</t>
+  </si>
+  <si>
+    <t>31-2025-12</t>
+  </si>
+  <si>
+    <t>12/2025/31</t>
+  </si>
+  <si>
+    <t>31/2025/12</t>
+  </si>
+  <si>
+    <t>31122025</t>
+  </si>
+  <si>
+    <t>20253112</t>
+  </si>
+  <si>
+    <t>12312025</t>
+  </si>
+  <si>
+    <t>20251231</t>
+  </si>
+  <si>
+    <t>31202512</t>
+  </si>
+  <si>
+    <t>12202531</t>
+  </si>
+  <si>
+    <t>31-12-2025</t>
+  </si>
+  <si>
+    <t>2024-31-10</t>
   </si>
 </sst>
 </file>
@@ -1833,4 +1945,227 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7B78349-5735-43F0-9D43-471341C2B224}">
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>166</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>169</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>170</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>171</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>173</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>174</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>175</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>176</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>